--- a/Building Relational Database/arquivos-pdf/Template_Normalizacao1.xlsx
+++ b/Building Relational Database/arquivos-pdf/Template_Normalizacao1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Salvio\FIAP\FIAP2022\FIAP_Presencial_Graduacao\1TDS_Building Relation Database\2o_Semestre\Aula_13_Normalizacao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\labsfiap\fiap-projetos-1tdspv\Building Relational Database\arquivos-pdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56095ED8-E06C-43AE-99FA-D6D6AD1215A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3047ADE-DAE8-4C83-9ACE-9FE164B63FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3F8E45FD-9A9B-458B-ABA8-7C1DEAD5F7CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{3F8E45FD-9A9B-458B-ABA8-7C1DEAD5F7CE}"/>
   </bookViews>
   <sheets>
     <sheet name="PedidoVenda" sheetId="1" r:id="rId1"/>
@@ -652,7 +652,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -949,18 +949,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECCEC4FB-088B-4DF2-8233-16BFCF3ED689}">
   <dimension ref="C2:I18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.109375" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:9" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="3:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:9" ht="13.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="3:9" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="3:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="44" t="s">
         <v>82</v>
       </c>
@@ -971,7 +971,7 @@
       <c r="H4" s="45"/>
       <c r="I4" s="46"/>
     </row>
-    <row r="5" spans="3:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:9" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="4" t="s">
         <v>0</v>
       </c>
@@ -986,7 +986,7 @@
       </c>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="3:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:9" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
         <v>3</v>
       </c>
@@ -999,7 +999,7 @@
       <c r="H6" s="5"/>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="3:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:9" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="7" t="s">
         <v>5</v>
       </c>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="3:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="10" t="s">
         <v>7</v>
       </c>
@@ -1025,7 +1025,7 @@
       <c r="H8" s="13"/>
       <c r="I8" s="14"/>
     </row>
-    <row r="9" spans="3:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="12" t="s">
         <v>9</v>
       </c>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="3:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:9" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -1055,7 +1055,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="3:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:9" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -1064,7 +1064,7 @@
       <c r="H11" s="2"/>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="3:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:9" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1073,7 +1073,7 @@
       <c r="H12" s="2"/>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="3:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:9" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -1082,7 +1082,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="3:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:9" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -1091,7 +1091,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="3:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:9" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -1100,7 +1100,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" spans="3:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:9" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1109,7 +1109,7 @@
       <c r="H16" s="2"/>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="3:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:9" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -1118,7 +1118,7 @@
       <c r="H17" s="2"/>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="3:9" s="15" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:9" s="15" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F18" s="12" t="s">
         <v>14</v>
       </c>
@@ -1139,26 +1139,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F489D7D7-72D8-44EF-B412-5EC787FA9562}">
   <dimension ref="B3:Q18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.5546875" customWidth="1"/>
-    <col min="2" max="2" width="7.77734375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="7.21875" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="41" customWidth="1"/>
-    <col min="12" max="12" width="15.33203125" customWidth="1"/>
-    <col min="13" max="13" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.88671875" style="16" customWidth="1"/>
-    <col min="16" max="16" width="13.6640625" customWidth="1"/>
-    <col min="17" max="17" width="14.88671875" customWidth="1"/>
+    <col min="12" max="12" width="15.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.85546875" style="16" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="33" t="s">
         <v>51</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="17">
         <v>11</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="17">
         <v>11</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="17">
         <v>11</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="23">
         <v>33</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="20">
         <v>65</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="20">
         <v>65</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="26">
         <v>78</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="26">
         <v>78</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="26">
         <v>78</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="18" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I18" s="41" t="s">
         <v>80</v>
       </c>
@@ -1680,22 +1680,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C73CFA48-B7B4-42E5-93DA-12D3114EB1D9}">
   <dimension ref="B3:K18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.5546875" customWidth="1"/>
-    <col min="2" max="2" width="7.77734375" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="41" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="33" t="s">
         <v>51</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="17">
         <v>11</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="23">
         <v>33</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="20">
         <v>65</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="26">
         <v>78</v>
       </c>
@@ -1855,8 +1855,8 @@
         <v>210</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:11" ht="45" x14ac:dyDescent="0.25">
       <c r="B9" s="33" t="s">
         <v>51</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="37">
         <v>11</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="37">
         <v>11</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="37">
         <v>11</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="38">
         <v>33</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="39">
         <v>65</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="39">
         <v>65</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="40">
         <v>78</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="40">
         <v>78</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="40">
         <v>78</v>
       </c>
@@ -2103,22 +2103,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B25352-371A-43DF-9764-F93F291B381E}">
   <dimension ref="B3:K24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.5546875" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
     <col min="4" max="4" width="12" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="41" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="33" t="s">
         <v>51</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="17">
         <v>11</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="23">
         <v>33</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="20">
         <v>65</v>
       </c>
@@ -2246,7 +2246,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="26">
         <v>78</v>
       </c>
@@ -2278,8 +2278,8 @@
         <v>210</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="33" t="s">
         <v>59</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="37">
         <v>11</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="37">
         <v>11</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="37">
         <v>11</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="38">
         <v>33</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="39">
         <v>65</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="39">
         <v>65</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="40">
         <v>78</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="40">
         <v>78</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="40">
         <v>78</v>
       </c>
@@ -2428,8 +2428,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="4.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
         <v>60</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="42">
         <v>34213</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="42">
         <v>65233</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="42">
         <v>76532</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="42">
         <v>89812</v>
       </c>
@@ -2510,30 +2510,30 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8972B8-8A12-4DDD-8051-36D4FADFF8D1}">
   <dimension ref="B1:R29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.5546875" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
     <col min="4" max="4" width="12" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.77734375" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.7109375" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="12.44140625" customWidth="1"/>
-    <col min="15" max="15" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="12.44140625" customWidth="1"/>
-    <col min="18" max="18" width="9.44140625" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="12.42578125" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="12.42578125" customWidth="1"/>
+    <col min="18" max="18" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="H1" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B3" s="33" t="s">
         <v>51</v>
       </c>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="G3" s="41"/>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="17">
         <v>11</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="23">
         <v>33</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="20">
         <v>65</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="26">
         <v>78</v>
       </c>
@@ -2619,8 +2619,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="33" t="s">
         <v>59</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="37">
         <v>11</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="37">
         <v>11</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="37">
         <v>11</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="38">
         <v>33</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="39">
         <v>65</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="39">
         <v>65</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="40">
         <v>78</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="40">
         <v>78</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="40">
         <v>78</v>
       </c>
@@ -2799,8 +2799,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="2:18" ht="4.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:18" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="34" t="s">
         <v>60</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="17">
         <v>89812</v>
       </c>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="R21" s="17"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="17">
         <v>76532</v>
       </c>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="R22" s="23"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="17">
         <v>34213</v>
       </c>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="R23" s="20"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B24" s="23">
         <v>89812</v>
       </c>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="R24" s="26"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="20">
         <v>76532</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B26" s="20">
         <v>65233</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="26">
         <v>89912</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="26">
         <v>65233</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="26">
         <v>34213</v>
       </c>
